--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428800</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428800</v>
       </c>
       <c r="B2" t="n">
-        <v>97336</v>
+        <v>97353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428800</v>
       </c>
       <c r="B2" t="n">
-        <v>97353</v>
+        <v>97370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428800</v>
       </c>
       <c r="B2" t="n">
-        <v>97370</v>
+        <v>97372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428800</v>
       </c>
       <c r="B2" t="n">
-        <v>97372</v>
+        <v>96960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 30828-2024 artfynd.xlsx
+++ b/artfynd/A 30828-2024 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Mikael Andersson</t>
+          <t>Mikael Andersson, Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
